--- a/examples/nurse_scheduling.xlsx
+++ b/examples/nurse_scheduling.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet name="workers" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="days" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="constraints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="constraints" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,28 +415,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>max_shifts_per_week</t>
+          <t>max_hours</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>available_days</t>
+          <t>skills</t>
         </is>
       </c>
     </row>
@@ -448,16 +442,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>RN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mon,Tue,Wed,Thu,Fri</t>
         </is>
       </c>
     </row>
@@ -468,16 +457,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>RN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mon,Tue,Thu,Fri,Sat</t>
         </is>
       </c>
     </row>
@@ -488,16 +472,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>RN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tue,Wed,Thu,Fri,Sun</t>
         </is>
       </c>
     </row>
@@ -508,16 +487,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>LPN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mon,Wed,Thu,Sat,Sun</t>
         </is>
       </c>
     </row>
@@ -528,16 +502,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>RN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mon,Tue,Wed,Fri,Sat</t>
         </is>
       </c>
     </row>
@@ -548,16 +517,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>LPN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tue,Wed,Thu,Fri,Sun</t>
         </is>
       </c>
     </row>
@@ -568,16 +532,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>RN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mon,Tue,Thu,Sat,Sun</t>
         </is>
       </c>
     </row>
@@ -588,16 +547,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>LPN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wed,Thu,Fri,Sat,Sun</t>
         </is>
       </c>
     </row>
@@ -612,38 +566,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>start_hour</t>
+          <t>duration_hours</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>end_hour</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>duration_hours</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>min_workers</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>required_role</t>
+          <t>required_workers</t>
         </is>
       </c>
     </row>
@@ -654,21 +593,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -678,21 +606,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -702,21 +619,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -730,178 +636,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-01-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-01-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>min_rest_hours</t>
+          <t>planning_horizon_days</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Min hours between consecutive shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_consecutive_days</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Max consecutive working days</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>weekend_coverage</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>At least 1 nurse per shift on weekends</t>
+          <t>Scheduling window: one week</t>
         </is>
       </c>
     </row>
